--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coihueco</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:03</t>
+    <t xml:space="preserve">2026-10-04 08:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:59</t>
+    <t xml:space="preserve">2026-10-05 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
